--- a/Proyecto_CBC/CBC (1).xlsx
+++ b/Proyecto_CBC/CBC (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbesze.ETRR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbesze.ETRR\.vscode\codigos-de-diagn-stico-santibesze\Proyecto_CBC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5353ACC-581C-4883-8E9E-F0E8672D82DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DD6BD7-CB88-4642-A9F3-5BB51CE2E7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="1170" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2970" yWindow="2450" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
